--- a/config/辅控/除湿机.xlsx
+++ b/config/辅控/除湿机.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -162,7 +162,7 @@
     <t>除湿设定点</t>
   </si>
   <si>
-    <t>dehumidificationSetPoint</t>
+    <t>dehumidifySetPoint</t>
   </si>
   <si>
     <t>{"en":"Dehumidification set point"}</t>
@@ -171,7 +171,7 @@
     <t>除湿回差</t>
   </si>
   <si>
-    <t>dehumidificationHysteresis</t>
+    <t>dehumidifyHysteresis</t>
   </si>
   <si>
     <t>{"en":"Dehumidification hysteresis"}</t>
